--- a/DataTables/DetailText/剧情/021结案.xlsx
+++ b/DataTables/DetailText/剧情/021结案.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2790CF64-73A6-4BF7-A285-9A6A2FE77C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7443D99D-9A0C-4E0F-A378-3C5076BE6313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>LineIndex</t>
   </si>
@@ -962,7 +962,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
